--- a/data/Study_dates_MeLiDos_MPI.xlsx
+++ b/data/Study_dates_MeLiDos_MPI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/WP2.2.5_Data_Analysis/GuidolinEtAl_Dataset_2025/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/GuidolinEtAl_Dataset_2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94F02C6-1DC0-EA4D-B472-7EE13E1CC68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1566FA5-B631-D94D-B25A-4B1880ECF4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="680" windowWidth="33460" windowHeight="21660" xr2:uid="{EB2C5E3B-016F-4147-BA32-349D8E1D3953}"/>
+    <workbookView xWindow="1460" yWindow="680" windowWidth="33460" windowHeight="21660" xr2:uid="{EB2C5E3B-016F-4147-BA32-349D8E1D3953}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="74">
   <si>
     <t>subjectID_device</t>
   </si>
@@ -178,6 +178,84 @@
   </si>
   <si>
     <t>datetime_trial_end timestamp from wearlog rather than "participant data sheet"</t>
+  </si>
+  <si>
+    <t>MPI_S201</t>
+  </si>
+  <si>
+    <t>MPI_S202</t>
+  </si>
+  <si>
+    <t>MPI_S203</t>
+  </si>
+  <si>
+    <t>MPI_S204</t>
+  </si>
+  <si>
+    <t>MPI_S205</t>
+  </si>
+  <si>
+    <t>MPI_S206</t>
+  </si>
+  <si>
+    <t>MPI_S207</t>
+  </si>
+  <si>
+    <t>MPI_S208</t>
+  </si>
+  <si>
+    <t>MPI_S209</t>
+  </si>
+  <si>
+    <t>MPI_S210</t>
+  </si>
+  <si>
+    <t>MPI_S211</t>
+  </si>
+  <si>
+    <t>MPI_S212</t>
+  </si>
+  <si>
+    <t>MPI_S213</t>
+  </si>
+  <si>
+    <t>MPI_S214</t>
+  </si>
+  <si>
+    <t>MPI_S215</t>
+  </si>
+  <si>
+    <t>MPI_S216</t>
+  </si>
+  <si>
+    <t>MPI_S217</t>
+  </si>
+  <si>
+    <t>MPI_S218</t>
+  </si>
+  <si>
+    <t>MPI_S219</t>
+  </si>
+  <si>
+    <t>MPI_S220</t>
+  </si>
+  <si>
+    <t>MPI_S221</t>
+  </si>
+  <si>
+    <t>MPI_S222</t>
+  </si>
+  <si>
+    <t>MPI_S223</t>
+  </si>
+  <si>
+    <t>MPI_S224</t>
+  </si>
+  <si>
+    <t>MPI_S225</t>
+  </si>
+  <si>
+    <t>MPI_S226</t>
   </si>
 </sst>
 </file>
@@ -690,8 +768,8 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="2">
-        <v>201</v>
+      <c r="A2" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="B2" s="2">
         <v>1020</v>
@@ -717,8 +795,8 @@
       <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="2">
-        <v>202</v>
+      <c r="A3" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="B3" s="2">
         <v>1382</v>
@@ -744,8 +822,8 @@
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="2">
-        <v>204</v>
+      <c r="A4" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="B4" s="2">
         <v>1740</v>
@@ -771,8 +849,8 @@
       <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="2">
-        <v>205</v>
+      <c r="A5" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B5" s="2">
         <v>1020</v>
@@ -798,8 +876,8 @@
       <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="2">
-        <v>206</v>
+      <c r="A6" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="B6" s="6">
         <v>1382</v>
@@ -825,8 +903,8 @@
       <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="2">
-        <v>208</v>
+      <c r="A7" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="B7" s="2">
         <v>1020</v>
@@ -852,8 +930,8 @@
       <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="2">
-        <v>209</v>
+      <c r="A8" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="B8" s="2">
         <v>1382</v>
@@ -879,8 +957,8 @@
       <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="2">
-        <v>210</v>
+      <c r="A9" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="B9" s="2">
         <v>1607</v>
@@ -906,8 +984,8 @@
       <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="2">
-        <v>212</v>
+      <c r="A10" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="B10" s="2">
         <v>1020</v>
@@ -933,8 +1011,8 @@
       <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="2">
-        <v>213</v>
+      <c r="A11" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="B11" s="2">
         <v>1382</v>
@@ -960,8 +1038,8 @@
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="2">
-        <v>214</v>
+      <c r="A12" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="B12" s="2">
         <v>1607</v>
@@ -989,8 +1067,8 @@
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="2">
-        <v>215</v>
+      <c r="A13" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="B13" s="2">
         <v>1020</v>
@@ -1016,8 +1094,8 @@
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="2">
-        <v>216</v>
+      <c r="A14" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="B14" s="2">
         <v>1382</v>
@@ -1043,8 +1121,8 @@
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="2">
-        <v>218</v>
+      <c r="A15" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="B15" s="2">
         <v>1020</v>
@@ -1072,8 +1150,8 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A16" s="2">
-        <v>219</v>
+      <c r="A16" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B16" s="2">
         <v>1382</v>
@@ -1101,8 +1179,8 @@
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="2">
-        <v>221</v>
+      <c r="A17" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="B17" s="2">
         <v>1607</v>
@@ -1130,8 +1208,8 @@
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="2">
-        <v>222</v>
+      <c r="A18" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="B18" s="2">
         <v>1020</v>
@@ -1157,8 +1235,8 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A19" s="2">
-        <v>223</v>
+      <c r="A19" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="B19" s="2">
         <v>2540</v>
@@ -1186,8 +1264,8 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A20" s="2">
-        <v>224</v>
+      <c r="A20" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="B20" s="2">
         <v>2663</v>
@@ -1215,8 +1293,8 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1">
-      <c r="A21" s="2">
-        <v>225</v>
+      <c r="A21" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="B21" s="2">
         <v>2793</v>
@@ -1244,8 +1322,8 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="2">
-        <v>226</v>
+      <c r="A22" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="B22" s="2">
         <v>1382</v>
@@ -1271,8 +1349,8 @@
       <c r="I22" s="7"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="2">
-        <v>227</v>
+      <c r="A23" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="B23" s="2">
         <v>1607</v>
@@ -1298,8 +1376,8 @@
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="2">
-        <v>228</v>
+      <c r="A24" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="B24" s="1">
         <v>1020</v>
@@ -1327,8 +1405,8 @@
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="2">
-        <v>229</v>
+      <c r="A25" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="B25" s="2">
         <v>2540</v>
@@ -1356,8 +1434,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A26" s="2">
-        <v>230</v>
+      <c r="A26" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="B26" s="2">
         <v>2663</v>
@@ -1385,8 +1463,8 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="2">
-        <v>231</v>
+      <c r="A27" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="B27" s="2">
         <v>2793</v>
